--- a/data/trans_bre/P19C08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C08-Edad-trans_bre.xlsx
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,53</t>
+          <t>-1,04; 0,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,12</t>
+          <t>-0,5; 1,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,49</t>
+          <t>-3,32; 1,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,41</t>
+          <t>-0,69; 1,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,25</t>
+          <t>-1,09; 1,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,08</t>
+          <t>-0,08; 0,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,74; 512,4</t>
+          <t>-85,28; 434,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,72</t>
+          <t>-0,7; 0,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,55</t>
+          <t>-0,28; 1,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,19</t>
+          <t>-0,36; 1,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,79</t>
+          <t>-0,96; 0,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,79; —</t>
+          <t>-72,47; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-83,25; 622,67</t>
+          <t>-83,41; —</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,91</t>
+          <t>-0,88; 0,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,03</t>
+          <t>-1,56; 1,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,68</t>
+          <t>-0,17; 0,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,0</t>
+          <t>-1,36; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,25</t>
+          <t>-1,8; 0,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,12</t>
+          <t>-1,17; 0,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,5</t>
+          <t>-1,06; 1,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,0</t>
+          <t>-2,32; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,0</t>
+          <t>-2,17; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,41</t>
+          <t>-1,04; 0,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -0,43</t>
+          <t>-4,55; -0,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,37</t>
+          <t>-1,37; 0,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,58</t>
+          <t>-0,16; 0,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,39</t>
+          <t>-0,46; 0,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,29</t>
+          <t>-0,15; 0,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,23</t>
+          <t>-0,5; 0,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 294,33</t>
+          <t>-37,19; 318,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,14; 98,65</t>
+          <t>-53,59; 89,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-84,06; 583,59</t>
+          <t>-83,28; 704,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-64,0; 93,55</t>
+          <t>-66,69; 84,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C08-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-22,92%</t>
+          <t>-23,46%</t>
         </is>
       </c>
     </row>
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,53</t>
+          <t>-1,03; 0,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,98</t>
+          <t>-0,56; 1,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,52</t>
+          <t>-2,94; 1,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>411,56%</t>
+          <t>-62,21%</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,29</t>
+          <t>-0,62; 1,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,09</t>
+          <t>-1,12; 1,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,99</t>
+          <t>-2,37; 0,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,28; 434,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,71</t>
+          <t>-0,71; 0,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,42</t>
+          <t>-0,37; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,25</t>
+          <t>-0,36; 1,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,84</t>
+          <t>-0,83; 0,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-72,47; —</t>
+          <t>-80,95; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-83,41; —</t>
+          <t>-82,35; 629,96</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>204,62%</t>
+          <t>111,47%</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,91</t>
+          <t>-0,9; 0,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,03</t>
+          <t>-1,67; 0,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,71</t>
+          <t>-0,34; 0,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-65,85%</t>
+          <t>-33,36%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,0</t>
+          <t>-1,45; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,24</t>
+          <t>-1,52; 0,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,14</t>
+          <t>-1,04; 0,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-38,87%</t>
+          <t>-5,87%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,5</t>
+          <t>-1,08; 1,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,0</t>
+          <t>-1,92; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,0</t>
+          <t>-2,01; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,36</t>
+          <t>-0,8; 0,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-47,01%</t>
+          <t>-47,92%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -0,44</t>
+          <t>-4,21; -0,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,37</t>
+          <t>-1,35; 0,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-15,38%</t>
+          <t>-16,26%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,57</t>
+          <t>-0,13; 0,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,37</t>
+          <t>-0,45; 0,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,3</t>
+          <t>-0,17; 0,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,23</t>
+          <t>-0,49; 0,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 318,01</t>
+          <t>-35,19; 304,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,59; 89,82</t>
+          <t>-52,5; 103,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-83,28; 704,03</t>
+          <t>-72,0; 772,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,69; 84,01</t>
+          <t>-60,89; 70,59</t>
         </is>
       </c>
     </row>
